--- a/public/templates/قالب-بيانات-الضرر.xlsx
+++ b/public/templates/قالب-بيانات-الضرر.xlsx
@@ -472,17 +472,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>أضرار جسيمة</t>
+          <t>ضرر شديد</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>أضرار متوسطة</t>
+          <t>ضرر متوسط</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>أضرار طفيفة</t>
+          <t>ضرر خفيف</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>عدد المباني في كل فئة: مدمر كلياً · أضرار جسيمة · أضرار متوسطة · أضرار طفيفة</t>
+          <t>عدد المباني في كل فئة: مدمر كلياً · ضرر شديد · ضرر متوسط · ضرر خفيف</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>تُستخدم في المعادلة الهندسية المعتمدة لتقدير الأنقاض: V = n × A × N × Cu × Bf</t>
+          <t>تُستخدم في المعادلة الهندسية المعتمدة لتقدير الأنقاض: المنهجية الأولى في الدليل المعتمد: المساحة × الطوابق × 3 م × معامل التحويل (0.35 / 0.20 / 0.08 / 0.02)</t>
         </is>
       </c>
     </row>
